--- a/002_A3/L2_analisis_caso/empleados_analisis_completo.xlsx
+++ b/002_A3/L2_analisis_caso/empleados_analisis_completo.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Empleados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen_Departamento" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen_Depto" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estadísticas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>depto</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -458,6 +458,16 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fecha_ingreso</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>año_ingreso</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mes_ingreso</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,12 @@
       <c r="E2" s="2" t="n">
         <v>44367</v>
       </c>
+      <c r="F2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -502,6 +518,12 @@
       <c r="E3" s="2" t="n">
         <v>44630</v>
       </c>
+      <c r="F3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -523,6 +545,12 @@
       <c r="E4" s="2" t="n">
         <v>44975</v>
       </c>
+      <c r="F4" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -544,6 +572,12 @@
       <c r="E5" s="2" t="n">
         <v>44576</v>
       </c>
+      <c r="F5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -564,6 +598,12 @@
       </c>
       <c r="E6" s="2" t="n">
         <v>44140</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -577,18 +617,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>depto</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Cantidad</t>
+          <t>Cantidad_Empleados</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -604,6 +644,11 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Salario_Máximo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Desv_Estándar</t>
         </is>
       </c>
     </row>
@@ -625,6 +670,7 @@
       <c r="E2" t="n">
         <v>48000</v>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -644,6 +690,7 @@
       <c r="E3" t="n">
         <v>46000</v>
       </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -663,6 +710,7 @@
       <c r="E4" t="n">
         <v>52000</v>
       </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -681,6 +729,9 @@
       </c>
       <c r="E5" t="n">
         <v>45000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
